--- a/TELEMETRYadcCLOCK/project/Address.xlsx
+++ b/TELEMETRYadcCLOCK/project/Address.xlsx
@@ -422,7 +422,7 @@
     <t>project_netlist_path</t>
   </si>
   <si>
-    <t>/tmp/kyle/mnt/celera/projects/Simplis/playcalum/Puget/Puget0/301A/overlay/SIMPLIS_Data/overlay_TELEMETRYadcCLOCK.net</t>
+    <t>/tmp/overlay_TELEMETRYadcCLOCK.net</t>
   </si>
   <si>
     <t>gen_reports</t>

--- a/TELEMETRYadcCLOCK/project/Address.xlsx
+++ b/TELEMETRYadcCLOCK/project/Address.xlsx
@@ -422,7 +422,7 @@
     <t>project_netlist_path</t>
   </si>
   <si>
-    <t>/tmp/overlay_TELEMETRYadcCLOCK.net</t>
+    <t>/tmp/kyle/mnt/celera/projects/Simplis/playcalum/Puget/Puget0/301A/overlay/SIMPLIS_Data/overlay_TELEMETRYadcCLOCK.net</t>
   </si>
   <si>
     <t>gen_reports</t>
